--- a/Session 9 - Interval Tree/DS Lab report sheet.xlsx
+++ b/Session 9 - Interval Tree/DS Lab report sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varin\Documents\Data Structure Git\Data-Structure-Library-1402\Session 9 - Interval Tree\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0D5807-1EBC-4525-85D0-88075697461E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B87DE9E-4372-46BB-A546-731B37C1C9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t xml:space="preserve">Student Name </t>
   </si>
@@ -58,9 +58,6 @@
     <t>(time scale, ms/sec/...)</t>
   </si>
   <si>
-    <t>محمدرضا امینی</t>
-  </si>
-  <si>
     <t>Windows 11</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
   </si>
   <si>
     <t>13th generation - 64 bit</t>
-  </si>
-  <si>
-    <t>سید محمد مهدی رضوی</t>
   </si>
   <si>
     <t>Treap with Interval</t>
@@ -225,23 +219,23 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -485,37 +479,29 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="27" customHeight="1">
-      <c r="A2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="9">
-        <v>402222020</v>
-      </c>
+      <c r="A2" s="6"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1">
-      <c r="A3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="9">
-        <v>402222073</v>
-      </c>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="13.2">
@@ -537,19 +523,19 @@
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="C6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="D6" s="9">
         <v>8</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="9">
         <v>4.5999999999999996</v>
       </c>
       <c r="F6" s="3"/>
@@ -575,10 +561,10 @@
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="9">
+      <c r="A9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="7">
         <v>200000</v>
       </c>
       <c r="C9" s="3"/>
@@ -587,115 +573,115 @@
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:8" ht="26.25" customHeight="1">
-      <c r="C10" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+      <c r="C10" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="26.25" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>28</v>
+      <c r="F11" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="6">
+        <v>2.9709782600402801</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6">
+        <v>9</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="F12" s="6">
+        <v>30471</v>
+      </c>
+      <c r="G12" s="6">
+        <v>780.21301746368397</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="22.5" customHeight="1">
+      <c r="A13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="6">
+        <v>3.27821516990661</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <v>11</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="F13" s="6">
+        <v>50269</v>
+      </c>
+      <c r="G13" s="6">
+        <v>975.88035178184498</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="22.5" customHeight="1">
+      <c r="A14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="8">
-        <v>2.9709782600402801</v>
-      </c>
-      <c r="C12" s="8">
+      <c r="B14" s="6">
+        <v>3.6146039962768501</v>
+      </c>
+      <c r="C14" s="6">
         <v>0</v>
       </c>
-      <c r="D12" s="8">
-        <v>9</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.52</v>
-      </c>
-      <c r="F12" s="8">
-        <v>30471</v>
-      </c>
-      <c r="G12" s="8">
-        <v>780.21301746368397</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A13" s="8" t="s">
+      <c r="D14" s="6">
+        <v>16</v>
+      </c>
+      <c r="E14" s="6">
+        <v>3.72</v>
+      </c>
+      <c r="F14" s="6">
+        <v>74472</v>
+      </c>
+      <c r="G14" s="6">
+        <v>910.25836038589398</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="B13" s="8">
-        <v>3.27821516990661</v>
-      </c>
-      <c r="C13" s="8">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8">
-        <v>11</v>
-      </c>
-      <c r="E13" s="8">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="F13" s="8">
-        <v>50269</v>
-      </c>
-      <c r="G13" s="8">
-        <v>975.88035178184498</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="8">
-        <v>3.6146039962768501</v>
-      </c>
-      <c r="C14" s="8">
-        <v>0</v>
-      </c>
-      <c r="D14" s="8">
-        <v>16</v>
-      </c>
-      <c r="E14" s="8">
-        <v>3.72</v>
-      </c>
-      <c r="F14" s="8">
-        <v>74472</v>
-      </c>
-      <c r="G14" s="8">
-        <v>910.25836038589398</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1"/>
